--- a/stories/arbres/ATOM-SOC.PAY.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Romane s'assoit près de papa. Ils ouvrent une boîte de cartes. Papa dit : on nomme un pays. Romane lit le nom : la Grèce. Elle répète : la Grèce. Sur la carte, de l'eau bleue. Papa dit : ça, c'est un paysage. C'est la mer. Romane dit : la mer. Autre carte : des sommets. Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
+          <t>Romane s'assoit près de papa. Ils ouvrent une boîte de cartes. On nomme un pays. Romane lit le nom : la Grèce. Elle répète : la Grèce. Sur la carte, de l'eau bleue. Ça, c'est un paysage. C'est la mer. La mer. Autre carte : des sommets. Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Romane s'assoit près de papa. Ils ouvrent une boîte de cartes.
+papa|On nomme un pays.
+narrateur|Romane lit le nom : la Grèce. Elle répète : la Grèce. Sur la carte, de l'eau bleue.
+papa|Ça, c'est un paysage. C'est la mer.
+enfant-f|La mer. Autre carte : des sommets.
+narrateur|Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Romane nomme la Grèce. Elle nomme aussi quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Romane a dit le nom. La Grèce. Elle a dit le paysage. La mer. La montagne aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Romane range les cartes. Papa ferme la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Romane nomme la Grèce. Elle nomme aussi quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Romane a dit le nom. La Grèce. Elle a dit le paysage. La mer. La montagne aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Romane range les cartes. Papa ferme la boîte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.PAY.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Romane nomme la Grèce et la mer</t>
+          <t>Le coquillage de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut entendre la mer de Grèce dans le coquillage, en regardant la photo bleue. Le coquillage roule. Ils le rattrapent. Le hush arrive.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Romane s'assoit près de papa. Ils ouvrent une boîte de cartes. On nomme un pays. Romane lit le nom : la Grèce. Elle répète : la Grèce. Sur la carte, de l'eau bleue. Ça, c'est un paysage. C'est la mer. La mer. Autre carte : des sommets. Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
+          <t>La lumière de midi rend le mur tout blanc. Un coquillage froid attend près de la fenêtre. Une photo bleue est coincée sous le cadre. Le rebord sent la poussière chaude. Nina vit ici, avec papa. Tu as vu le coquillage, Nina ? Il est froid. Oui. Il vient de la Grèce. En ce moment, Nina prend la photo. Le papier est lisse et un peu gondolé. Tout bleu. C'est la mer de Grèce. La Grèce. Et la mer. Un pays. Un paysage. Nina pose la photo contre le verre. Le bleu du papier rejoint le ciel. Je veux entendre la mer. Dans le coquillage. Tu le mets à l'oreille ? Oui. Nina lève le coquillage. La coquille glisse entre ses doigts. Elle roule sur le rebord. Il part ! Doucement. On le rattrape. Papa tend la main. Nina tend la sienne aussi. Le coquillage s'arrête contre un caillou. Il a failli tomber. Il est là. Tu le reprends ? Oui, papa. La coquille est encore plus froide. Nina la serre des deux mains. À l'oreille, maintenant. Nina pose la coquille contre sa joue. Je n'entends rien. Tourne-le un peu. L'ouverture vers toi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Romane s'assoit près de papa. Ils ouvrent une boîte de cartes. Papa dit : on &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un pays. Romane lit le nom : la Grèce. Elle répète : la Grèce. Sur la carte, de l'eau bleue. Papa dit : ça, c'est un paysage. C'est la mer. Romane dit : la mer. Autre carte : des sommets. Un paysage. La montagne. Un pays. Un nom. Un paysage.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lumière de midi rend le mur tout blanc. Un coquillage froid attend près de la fenêtre. Une photo bleue est coincée sous le cadre. Le rebord sent la poussière chaude. Nina vit ici, avec papa. Tu as vu le coquillage, Nina ? Il est froid. Oui. Il vient de la Grèce. En ce moment, Nina prend la photo. Le papier est lisse et un peu gondolé. Tout bleu. C'est la mer de Grèce. La Grèce. Et la mer. Un pays. Un paysage. Nina pose la photo contre le verre. Le bleu du papier rejoint le ciel. Je veux entendre la mer. Dans le coquillage. Tu le mets à l'oreille ? Oui. Nina lève le coquillage. La coquille glisse entre ses doigts. Elle roule sur le rebord. Il part ! Doucement. On le rattrape. Papa tend la main. Nina tend la sienne aussi. Le coquillage s'arrête contre un caillou. Il a failli tomber. Il est là. Tu le reprends ? Oui, papa. La coquille est encore plus froide. Nina la serre des deux mains. À l'oreille, maintenant. Nina pose la coquille contre sa joue. Je n'entends rien. Tourne-le un peu. L'ouverture vers toi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Romane s'assoit près de papa. Ils ouvrent une boîte de cartes.
-papa|On nomme un pays.
-narrateur|Romane lit le nom : la Grèce. Elle répète : la Grèce. Sur la carte, de l'eau bleue.
-papa|Ça, c'est un paysage. C'est la mer.
-enfant-f|La mer. Autre carte : des sommets.
-narrateur|Un paysage. La montagne. Un pays. Un nom. Un paysage.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La lumière de midi rend le mur tout blanc.
+narrateur|Un coquillage froid attend près de la fenêtre.
+narrateur|Une photo bleue est coincée sous le cadre.
+narrateur|Le rebord sent la poussière chaude.
+narrateur|Nina vit ici, avec papa.
+papa|Tu as vu le coquillage, Nina ?
+enfant-f|Il est froid.
+papa|Oui.
+papa|Il vient de la Grèce.
+narrateur|En ce moment, Nina prend la photo.
+narrateur|Le papier est lisse et un peu gondolé.
+enfant-f|Tout bleu.
+papa|C'est la mer de Grèce.
+enfant-f|La Grèce.
+enfant-f|Et la mer.
+papa|Un pays.
+papa|Un paysage.
+narrateur|Nina pose la photo contre le verre.
+narrateur|Le bleu du papier rejoint le ciel.
+enfant-f|Je veux entendre la mer.
+enfant-f|Dans le coquillage.
+papa|Tu le mets à l'oreille ?
+enfant-f|Oui.
+narrateur|Nina lève le coquillage.
+narrateur|La coquille glisse entre ses doigts.
+narrateur|Elle roule sur le rebord.
+enfant-f|Il part !
+papa|Doucement.
+papa|On le rattrape.
+narrateur|Papa tend la main.
+narrateur|Nina tend la sienne aussi.
+narrateur|Le coquillage s'arrête contre un caillou.
+enfant-f|Il a failli tomber.
+papa|Il est là.
+papa|Tu le reprends ?
+enfant-f|Oui, papa.
+narrateur|La coquille est encore plus froide.
+narrateur|Nina la serre des deux mains.
+papa|À l'oreille, maintenant.
+narrateur|Nina pose la coquille contre sa joue.
+enfant-f|Je n'entends rien.
+papa|Tourne-le un peu.
+papa|L'ouverture vers toi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1393,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Romane nomme la Grèce. Elle nomme aussi quoi ?</t>
+          <t>Nina nomme la Grèce. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Romane &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me la Grèce. Elle nomme aussi quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina nomme la Grèce. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1413,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la mer | un paysage | un pays | la Grèce</t>
+          <t>mer | la mer | mer de Grèce | hush | l'eau</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1428,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a de l'eau bleue. C'est quel paysage ?</t>
+          <t>Nina nomme aussi la mer. Elle nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1422,14 +1470,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1553,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Romane nomme la Grèce. Elle nomme aussi quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina nomme la Grèce.
+narrateur|Elle nomme aussi quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1581,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Romane a dit le nom. La Grèce. Elle a dit le paysage. La mer. La montagne aussi.</t>
+          <t>Nina tourne le coquillage. L'ouverture touche son oreille. Chhh. J'entends ! Oui. Comme la mer. Le hush est doux, tout près. Nina regarde la photo en même temps. La mer de Grèce. Tu l'entends, et tu la vois. Merci, Nina. Elle tient le coquillage plus fort. Le rebord n'a plus de place pour rouler. On le pose dans le creux. Ici, près de la photo. Le bleu du papier touche la coquille. Froid contre lisse. Ils sont ensemble. La Grèce, tout près.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Romane a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;. La Grèce. Elle a dit le paysage. La mer. La montagne aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina tourne le coquillage. L'ouverture touche son oreille. Chhh. J'entends ! Oui. Comme la mer. Le hush est doux, tout près. Nina regarde la photo en même temps. La mer de Grèce. Tu l'entends, et tu la vois. Merci, Nina. Elle tient le coquillage plus fort. Le rebord n'a plus de place pour rouler. On le pose dans le creux. Ici, près de la photo. Le bleu du papier touche la coquille. Froid contre lisse. Ils sont ensemble. La Grèce, tout près.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1601,7 +1649,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1677,10 +1725,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Romane a dit le nom. La Grèce. Elle a dit le paysage. La mer. La montagne aussi.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina tourne le coquillage.
+narrateur|L'ouverture touche son oreille.
+enfant-f|Chhh.
+enfant-f|J'entends !
+papa|Oui.
+papa|Comme la mer.
+narrateur|Le hush est doux, tout près.
+narrateur|Nina regarde la photo en même temps.
+enfant-f|La mer de Grèce.
+papa|Tu l'entends, et tu la vois.
+papa|Merci, Nina.
+narrateur|Elle tient le coquillage plus fort.
+narrateur|Le rebord n'a plus de place pour rouler.
+papa|On le pose dans le creux.
+enfant-f|Ici, près de la photo.
+narrateur|Le bleu du papier touche la coquille.
+narrateur|Froid contre lisse.
+enfant-f|Ils sont ensemble.
+papa|La Grèce, tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,12 +1770,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Romane range les cartes. Papa ferme la boîte.</t>
+          <t>Tu as fini d'écouter ? Encore un peu. Nina remet la coquille à l'oreille. Le hush revient, plus bas. La mer est petite, dedans. Et grande, sur la photo. Un nuage passe sur le mur blanc. Le bleu de la photo reste. La Grèce. La mer. Oui. Nina pose enfin le coquillage. Il ne roule plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Romane range les cartes. Papa ferme la boîte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu as fini d'écouter ? Encore un peu. Nina remet la coquille à l'oreille. Le hush revient, plus bas. La mer est petite, dedans. Et grande, sur la photo. Un nuage passe sur le mur blanc. Le bleu de la photo reste. La Grèce. La mer. Oui. Nina pose enfin le coquillage. Il ne roule plus.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1773,7 +1838,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1841,10 +1906,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Romane range les cartes. Papa ferme la boîte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>papa|Tu as fini d'écouter ?
+enfant-f|Encore un peu.
+narrateur|Nina remet la coquille à l'oreille.
+narrateur|Le hush revient, plus bas.
+enfant-f|La mer est petite, dedans.
+papa|Et grande, sur la photo.
+narrateur|Un nuage passe sur le mur blanc.
+narrateur|Le bleu de la photo reste.
+enfant-f|La Grèce.
+enfant-f|La mer.
+papa|Oui.
+narrateur|Nina pose enfin le coquillage.
+narrateur|Il ne roule plus.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La photo bleue garde son gondolement. Le coquillage reste dans le creux. J'ai entendu la mer. Elle est encore là, si tu colles l'oreille. Le mur blanc redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La photo bleue garde son gondolement. Le coquillage reste dans le creux. J'ai entendu la mer. Elle est encore là, si tu colles l'oreille. Le mur blanc redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,7 +2013,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2009,10 +2085,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La photo bleue garde son gondolement.
+narrateur|Le coquillage reste dans le creux.
+enfant-f|J'ai entendu la mer.
+papa|Elle est encore là, si tu colles l'oreille.
+narrateur|Le mur blanc redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>rebord de fenêtre, lumière de midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Romane, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
